--- a/analysis/dataview/code.xlsx
+++ b/analysis/dataview/code.xlsx
@@ -9,16 +9,17 @@
   <sheets>
     <sheet name="Unique Variants" sheetId="1" r:id="rId1"/>
     <sheet name="SubTask" sheetId="2" r:id="rId2"/>
-    <sheet name="ModelFamily" sheetId="3" r:id="rId3"/>
-    <sheet name="ModelName" sheetId="4" r:id="rId4"/>
-    <sheet name="CodeType" sheetId="5" r:id="rId5"/>
+    <sheet name="ExampleType" sheetId="3" r:id="rId3"/>
+    <sheet name="ModelFamily" sheetId="4" r:id="rId4"/>
+    <sheet name="ModelName" sheetId="5" r:id="rId5"/>
+    <sheet name="CodeType" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="47">
   <si>
     <t>Unique Variants</t>
   </si>
@@ -51,6 +52,18 @@
   </si>
   <si>
     <t>TimeComplexity</t>
+  </si>
+  <si>
+    <t>FewShot</t>
+  </si>
+  <si>
+    <t>OneShot</t>
+  </si>
+  <si>
+    <t>ZeroShot</t>
+  </si>
+  <si>
+    <t>max</t>
   </si>
   <si>
     <t>01-ai</t>
@@ -525,7 +538,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -611,12 +624,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>6</v>
@@ -633,13 +646,13 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>66.75</v>
+        <v>57.3</v>
       </c>
       <c r="C2">
-        <v>4.787135538781691</v>
+        <v>10.14162864528905</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -647,10 +660,10 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>45.29166666666666</v>
+        <v>48.70833333333334</v>
       </c>
       <c r="C3">
-        <v>27.62242184179</v>
+        <v>22.33048056623145</v>
       </c>
       <c r="D3">
         <v>24</v>
@@ -661,111 +674,13 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>66.5</v>
+        <v>51.05</v>
       </c>
       <c r="C4">
-        <v>5.196152422706634</v>
+        <v>25.55175346748551</v>
       </c>
       <c r="D4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5">
-        <v>0.25</v>
-      </c>
-      <c r="C5">
-        <v>0.5</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6">
-        <v>72.5</v>
-      </c>
-      <c r="C6">
-        <v>4.654746681256313</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7">
-        <v>65.75</v>
-      </c>
-      <c r="C7">
-        <v>4.787135538781691</v>
-      </c>
-      <c r="D7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8">
-        <v>61.15</v>
-      </c>
-      <c r="C8">
-        <v>11.30568091945954</v>
-      </c>
-      <c r="D8">
         <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9">
-        <v>65.25</v>
-      </c>
-      <c r="C9">
-        <v>4.99165971062398</v>
-      </c>
-      <c r="D9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10">
-        <v>58.75</v>
-      </c>
-      <c r="C10">
-        <v>3.5</v>
-      </c>
-      <c r="D10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11">
-        <v>68.625</v>
-      </c>
-      <c r="C11">
-        <v>4.470139019889968</v>
-      </c>
-      <c r="D11">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -775,301 +690,224 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>4</v>
-      </c>
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <v>66.75</v>
+      </c>
+      <c r="D2">
+        <v>4.787135538781691</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>66.75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>45.29166666666666</v>
+      </c>
+      <c r="D3">
+        <v>27.62242184179</v>
+      </c>
+      <c r="E3">
+        <v>24</v>
+      </c>
+      <c r="F3">
+        <v>69.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>66.5</v>
+      </c>
+      <c r="D4">
+        <v>5.196152422706634</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>64.83333333333333</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5">
+        <v>0.25</v>
+      </c>
+      <c r="D5">
+        <v>0.5</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6">
+        <v>72.5</v>
+      </c>
+      <c r="D6">
+        <v>4.654746681256313</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>72.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>65.75</v>
+      </c>
+      <c r="D7">
+        <v>4.787135538781691</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>65.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="B2">
-        <v>0.25</v>
-      </c>
-      <c r="C2">
-        <v>0.5</v>
-      </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="C8">
+        <v>61.15</v>
+      </c>
+      <c r="D8">
+        <v>11.30568091945954</v>
+      </c>
+      <c r="E8">
+        <v>20</v>
+      </c>
+      <c r="F8">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="B3">
-        <v>70.5</v>
-      </c>
-      <c r="C3">
-        <v>3.785938897200183</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="C9">
+        <v>65.25</v>
+      </c>
+      <c r="D9">
+        <v>4.99165971062398</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>65.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
         <v>23</v>
       </c>
-      <c r="B4">
-        <v>68.75</v>
-      </c>
-      <c r="C4">
-        <v>3.304037933599834</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="C10">
+        <v>58.75</v>
+      </c>
+      <c r="D10">
+        <v>3.5</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="F10">
+        <v>58.75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
         <v>24</v>
       </c>
-      <c r="B5">
-        <v>44.25</v>
-      </c>
-      <c r="C5">
-        <v>13.04798835069989</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6">
-        <v>60.5</v>
-      </c>
-      <c r="C6">
-        <v>5.507570547286102</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7">
-        <v>61.75</v>
-      </c>
-      <c r="C7">
-        <v>2.872281323269013</v>
-      </c>
-      <c r="D7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8">
-        <v>58.75</v>
-      </c>
-      <c r="C8">
-        <v>3.5</v>
-      </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9">
-        <v>65.25</v>
-      </c>
-      <c r="C9">
-        <v>4.99165971062398</v>
-      </c>
-      <c r="D9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10">
-        <v>2.5</v>
-      </c>
-      <c r="C10">
-        <v>1.290994448735805</v>
-      </c>
-      <c r="D10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11">
-        <v>56.75</v>
-      </c>
       <c r="C11">
-        <v>3.5</v>
+        <v>68.625</v>
       </c>
       <c r="D11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12">
-        <v>13.75</v>
-      </c>
-      <c r="C12">
-        <v>4.112987559751022</v>
-      </c>
-      <c r="D12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13">
-        <v>60.25</v>
-      </c>
-      <c r="C13">
-        <v>4.272001872658764</v>
-      </c>
-      <c r="D13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14">
-        <v>69.25</v>
-      </c>
-      <c r="C14">
-        <v>3.403429642777024</v>
-      </c>
-      <c r="D14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15">
-        <v>69.25</v>
-      </c>
-      <c r="C15">
-        <v>4.112987559751022</v>
-      </c>
-      <c r="D15">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16">
-        <v>66.75</v>
-      </c>
-      <c r="C16">
-        <v>4.787135538781691</v>
-      </c>
-      <c r="D16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17">
-        <v>72.5</v>
-      </c>
-      <c r="C17">
-        <v>4.654746681256313</v>
-      </c>
-      <c r="D17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18">
-        <v>66.5</v>
-      </c>
-      <c r="C18">
-        <v>5.196152422706634</v>
-      </c>
-      <c r="D18">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19">
-        <v>66.5</v>
-      </c>
-      <c r="C19">
-        <v>3.109126351029605</v>
-      </c>
-      <c r="D19">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20">
+        <v>4.470139019889968</v>
+      </c>
+      <c r="E11">
+        <v>8</v>
+      </c>
+      <c r="F11">
         <v>70.75</v>
-      </c>
-      <c r="C20">
-        <v>4.99165971062398</v>
-      </c>
-      <c r="D20">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21">
-        <v>65.75</v>
-      </c>
-      <c r="C21">
-        <v>4.787135538781691</v>
-      </c>
-      <c r="D21">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1079,6 +917,310 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2">
+        <v>0.25</v>
+      </c>
+      <c r="C2">
+        <v>0.5</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3">
+        <v>70.5</v>
+      </c>
+      <c r="C3">
+        <v>3.785938897200183</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4">
+        <v>68.75</v>
+      </c>
+      <c r="C4">
+        <v>3.304037933599834</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5">
+        <v>44.25</v>
+      </c>
+      <c r="C5">
+        <v>13.04798835069989</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6">
+        <v>60.5</v>
+      </c>
+      <c r="C6">
+        <v>5.507570547286102</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7">
+        <v>61.75</v>
+      </c>
+      <c r="C7">
+        <v>2.872281323269013</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8">
+        <v>58.75</v>
+      </c>
+      <c r="C8">
+        <v>3.5</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>65.25</v>
+      </c>
+      <c r="C9">
+        <v>4.99165971062398</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10">
+        <v>2.5</v>
+      </c>
+      <c r="C10">
+        <v>1.290994448735805</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11">
+        <v>56.75</v>
+      </c>
+      <c r="C11">
+        <v>3.5</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12">
+        <v>13.75</v>
+      </c>
+      <c r="C12">
+        <v>4.112987559751022</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13">
+        <v>60.25</v>
+      </c>
+      <c r="C13">
+        <v>4.272001872658764</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14">
+        <v>69.25</v>
+      </c>
+      <c r="C14">
+        <v>3.403429642777024</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15">
+        <v>69.25</v>
+      </c>
+      <c r="C15">
+        <v>4.112987559751022</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16">
+        <v>66.75</v>
+      </c>
+      <c r="C16">
+        <v>4.787135538781691</v>
+      </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17">
+        <v>72.5</v>
+      </c>
+      <c r="C17">
+        <v>4.654746681256313</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18">
+        <v>66.5</v>
+      </c>
+      <c r="C18">
+        <v>5.196152422706634</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19">
+        <v>66.5</v>
+      </c>
+      <c r="C19">
+        <v>3.109126351029605</v>
+      </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20">
+        <v>70.75</v>
+      </c>
+      <c r="C20">
+        <v>4.99165971062398</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21">
+        <v>65.75</v>
+      </c>
+      <c r="C21">
+        <v>4.787135538781691</v>
+      </c>
+      <c r="D21">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1098,7 +1240,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B2">
         <v>57.875</v>
@@ -1112,7 +1254,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B3">
         <v>53.175</v>
